--- a/did.xlsx
+++ b/did.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\oqc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA986E2-F3DA-44BF-9CA5-B767802D8276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3975" yWindow="2640" windowWidth="20640" windowHeight="6255" activeTab="5"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-08-2026" sheetId="340" r:id="rId1"/>
@@ -14,7 +20,8 @@
     <sheet name="05-08-2026" sheetId="345" r:id="rId5"/>
     <sheet name="06-08-2026" sheetId="346" r:id="rId6"/>
     <sheet name="07-08-2026" sheetId="347" r:id="rId7"/>
-    <sheet name="Sheet2" sheetId="336" r:id="rId8"/>
+    <sheet name="08-08-2026" sheetId="336" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="348" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-08-2026'!$A$5:$I$5</definedName>
@@ -25,12 +32,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06-08-2026'!$A$5:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'07-08-2026'!$A$5:$I$5</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="149">
   <si>
     <t>No</t>
   </si>
@@ -482,11 +489,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -732,7 +739,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -740,25 +747,25 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -786,10 +793,9 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -814,13 +820,13 @@
     <xf numFmtId="1" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -832,7 +838,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="11" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -853,7 +859,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -871,13 +877,16 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="표준_1st BOM_Bom List _ MODEL LHS-25SC_REV" xfId="1"/>
+    <cellStyle name="표준_1st BOM_Bom List _ MODEL LHS-25SC_REV" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -926,7 +935,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -959,9 +968,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -994,6 +1020,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1169,68 +1212,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="55.7109375" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" style="17" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" customWidth="1"/>
+    <col min="3" max="3" width="55.7265625" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" customWidth="1"/>
+    <col min="6" max="6" width="21.26953125" customWidth="1"/>
+    <col min="7" max="7" width="18.54296875" style="17" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="43.42578125" customWidth="1"/>
+    <col min="9" max="9" width="43.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="40"/>
-    </row>
-    <row r="2" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="43"/>
-    </row>
-    <row r="4" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="46"/>
-    </row>
-    <row r="5" spans="1:9" ht="55.5" customHeight="1">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
+    </row>
+    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="45"/>
+    </row>
+    <row r="5" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -1259,7 +1302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="47.25" customHeight="1">
+    <row r="6" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -1286,7 +1329,7 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:9" ht="47.25" customHeight="1">
+    <row r="7" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -1313,7 +1356,7 @@
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9" ht="47.25" customHeight="1">
+    <row r="8" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -1340,7 +1383,7 @@
       </c>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="47.25" customHeight="1">
+    <row r="9" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -1367,7 +1410,7 @@
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="10" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -1394,7 +1437,7 @@
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="11" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -1421,7 +1464,7 @@
       </c>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="12" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -1448,7 +1491,7 @@
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="13" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -1475,7 +1518,7 @@
       </c>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="14" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -1502,7 +1545,7 @@
       </c>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="15" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -1529,7 +1572,7 @@
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="16" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -1556,7 +1599,7 @@
       </c>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="17" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -1583,7 +1626,7 @@
       </c>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="18" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -1610,7 +1653,7 @@
       </c>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="19" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -1637,7 +1680,7 @@
       </c>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="20" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -1664,14 +1707,14 @@
       </c>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="21" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>16</v>
       </c>
       <c r="B21" s="19">
         <v>187314901</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="28" t="s">
         <v>44</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -1691,7 +1734,7 @@
       </c>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="22" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>17</v>
       </c>
@@ -1720,7 +1763,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="23" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>18</v>
       </c>
@@ -1749,17 +1792,17 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="24" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>19</v>
       </c>
       <c r="B24" s="19">
         <v>186778701</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="30" t="s">
         <v>112</v>
       </c>
       <c r="E24" s="6">
@@ -1778,17 +1821,17 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="25" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>20</v>
       </c>
       <c r="B25" s="19">
         <v>186778900</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D25" s="30" t="s">
         <v>112</v>
       </c>
       <c r="E25" s="6">
@@ -1807,7 +1850,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="26" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>21</v>
       </c>
@@ -1834,7 +1877,7 @@
       </c>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="27" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>22</v>
       </c>
@@ -1857,7 +1900,7 @@
       </c>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="28" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>23</v>
       </c>
@@ -1867,7 +1910,7 @@
       <c r="C28" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="31" t="s">
         <v>112</v>
       </c>
       <c r="E28" s="13">
@@ -1886,7 +1929,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="29" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>24</v>
       </c>
@@ -1896,7 +1939,7 @@
       <c r="C29" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="31" t="s">
         <v>112</v>
       </c>
       <c r="E29" s="13">
@@ -1915,7 +1958,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="30" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>25</v>
       </c>
@@ -1944,36 +1987,36 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
-      <c r="A31" s="22">
+    <row r="31" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="21">
         <v>26</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="22">
         <v>196870802</v>
       </c>
-      <c r="C31" s="30" t="s">
+      <c r="C31" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="E31" s="26">
-        <v>1</v>
-      </c>
-      <c r="F31" s="27">
+      <c r="E31" s="25">
+        <v>1</v>
+      </c>
+      <c r="F31" s="26">
         <v>46235</v>
       </c>
-      <c r="G31" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H31" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I31" s="21" t="s">
+      <c r="G31" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="32" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>27</v>
       </c>
@@ -1983,7 +2026,7 @@
       <c r="C32" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="31" t="s">
         <v>112</v>
       </c>
       <c r="E32" s="13">
@@ -2000,7 +2043,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="33" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>28</v>
       </c>
@@ -2010,7 +2053,7 @@
       <c r="C33" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="31" t="s">
         <v>112</v>
       </c>
       <c r="E33" s="13">
@@ -2027,7 +2070,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="34" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>29</v>
       </c>
@@ -2037,7 +2080,7 @@
       <c r="C34" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="31" t="s">
         <v>112</v>
       </c>
       <c r="E34" s="13">
@@ -2054,7 +2097,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="35" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <v>30</v>
       </c>
@@ -2064,7 +2107,7 @@
       <c r="C35" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="31" t="s">
         <v>112</v>
       </c>
       <c r="E35" s="13">
@@ -2081,7 +2124,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="36" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>31</v>
       </c>
@@ -2091,7 +2134,7 @@
       <c r="C36" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="31" t="s">
         <v>112</v>
       </c>
       <c r="E36" s="13">
@@ -2108,7 +2151,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="37" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>32</v>
       </c>
@@ -2118,7 +2161,7 @@
       <c r="C37" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="31" t="s">
         <v>112</v>
       </c>
       <c r="E37" s="13">
@@ -2135,7 +2178,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="38" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>33</v>
       </c>
@@ -2145,7 +2188,7 @@
       <c r="C38" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="31" t="s">
         <v>112</v>
       </c>
       <c r="E38" s="13">
@@ -2162,7 +2205,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="39" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>34</v>
       </c>
@@ -2172,7 +2215,7 @@
       <c r="C39" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="31" t="s">
         <v>112</v>
       </c>
       <c r="E39" s="13">
@@ -2189,7 +2232,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="40" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <v>35</v>
       </c>
@@ -2199,7 +2242,7 @@
       <c r="C40" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="31" t="s">
         <v>112</v>
       </c>
       <c r="E40" s="13">
@@ -2216,7 +2259,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="41" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>36</v>
       </c>
@@ -2245,7 +2288,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="42" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>37</v>
       </c>
@@ -2274,7 +2317,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="43" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>38</v>
       </c>
@@ -2303,7 +2346,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="20" customFormat="1" ht="52.5" customHeight="1">
+    <row r="44" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>39</v>
       </c>
@@ -2332,7 +2375,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="45" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>40</v>
       </c>
@@ -2361,7 +2404,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="46" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10">
         <v>41</v>
       </c>
@@ -2388,7 +2431,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="47" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10">
         <v>42</v>
       </c>
@@ -2398,7 +2441,7 @@
       <c r="C47" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="31" t="s">
         <v>112</v>
       </c>
       <c r="E47" s="13">
@@ -2415,7 +2458,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="48" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10">
         <v>43</v>
       </c>
@@ -2442,7 +2485,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="49" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10">
         <v>44</v>
       </c>
@@ -2469,7 +2512,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="50" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10">
         <v>45</v>
       </c>
@@ -2496,7 +2539,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="51" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>46</v>
       </c>
@@ -2516,7 +2559,7 @@
       <c r="I51" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I5"/>
+  <autoFilter ref="A5:I5" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I4"/>
   </mergeCells>
@@ -2527,68 +2570,68 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="55.7109375" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" style="17" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" customWidth="1"/>
+    <col min="3" max="3" width="55.7265625" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" customWidth="1"/>
+    <col min="6" max="6" width="21.26953125" customWidth="1"/>
+    <col min="7" max="7" width="18.54296875" style="17" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="43.42578125" customWidth="1"/>
+    <col min="9" max="9" width="43.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="40"/>
-    </row>
-    <row r="2" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="43"/>
-    </row>
-    <row r="4" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="46"/>
-    </row>
-    <row r="5" spans="1:9" ht="55.5" customHeight="1">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
+    </row>
+    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="45"/>
+    </row>
+    <row r="5" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -2617,7 +2660,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="47.25" customHeight="1">
+    <row r="6" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -2644,7 +2687,7 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:9" ht="47.25" customHeight="1">
+    <row r="7" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -2671,7 +2714,7 @@
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9" ht="47.25" customHeight="1">
+    <row r="8" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -2698,7 +2741,7 @@
       </c>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="47.25" customHeight="1">
+    <row r="9" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -2725,7 +2768,7 @@
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="10" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -2752,7 +2795,7 @@
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="11" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -2779,7 +2822,7 @@
       </c>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="12" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -2806,7 +2849,7 @@
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="13" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -2833,14 +2876,14 @@
       </c>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="14" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>9</v>
       </c>
       <c r="B14" s="19">
         <v>186778701</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="28" t="s">
         <v>35</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -2860,14 +2903,14 @@
       </c>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="15" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>10</v>
       </c>
       <c r="B15" s="19">
         <v>186778900</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="28" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="5" t="s">
@@ -2887,7 +2930,7 @@
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="16" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -2914,7 +2957,7 @@
       </c>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="17" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -2937,7 +2980,7 @@
       </c>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="18" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -2964,7 +3007,7 @@
       </c>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="19" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -2991,7 +3034,7 @@
       </c>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="20" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -3018,7 +3061,7 @@
       </c>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="21" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>16</v>
       </c>
@@ -3047,7 +3090,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="22" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>17</v>
       </c>
@@ -3076,7 +3119,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="23" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>18</v>
       </c>
@@ -3105,7 +3148,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="24" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>19</v>
       </c>
@@ -3134,7 +3177,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="25" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>20</v>
       </c>
@@ -3163,7 +3206,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="26" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>21</v>
       </c>
@@ -3192,36 +3235,36 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
-      <c r="A27" s="22">
+    <row r="27" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="21">
         <v>22</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="22">
         <v>196870802</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C27" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="D27" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="26">
-        <v>1</v>
-      </c>
-      <c r="F27" s="27">
+      <c r="E27" s="25">
+        <v>1</v>
+      </c>
+      <c r="F27" s="26">
         <v>46236</v>
       </c>
-      <c r="G27" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H27" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I27" s="21" t="s">
+      <c r="G27" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="28" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>23</v>
       </c>
@@ -3250,7 +3293,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="29" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>24</v>
       </c>
@@ -3277,7 +3320,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="30" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>25</v>
       </c>
@@ -3304,7 +3347,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="31" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>26</v>
       </c>
@@ -3331,7 +3374,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="32" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>27</v>
       </c>
@@ -3358,7 +3401,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="33" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>28</v>
       </c>
@@ -3385,7 +3428,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="34" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>29</v>
       </c>
@@ -3412,7 +3455,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="35" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <v>30</v>
       </c>
@@ -3439,7 +3482,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="36" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>31</v>
       </c>
@@ -3466,7 +3509,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="37" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>32</v>
       </c>
@@ -3493,7 +3536,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="38" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>33</v>
       </c>
@@ -3520,7 +3563,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="39" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>34</v>
       </c>
@@ -3547,7 +3590,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="40" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <v>35</v>
       </c>
@@ -3574,7 +3617,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="41" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10">
         <v>36</v>
       </c>
@@ -3601,7 +3644,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="42" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>37</v>
       </c>
@@ -3628,7 +3671,7 @@
       </c>
       <c r="I42" s="9"/>
     </row>
-    <row r="43" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="43" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>38</v>
       </c>
@@ -3648,7 +3691,7 @@
       <c r="I43" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I5"/>
+  <autoFilter ref="A5:I5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I4"/>
   </mergeCells>
@@ -3659,68 +3702,68 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="55.7109375" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" style="17" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" customWidth="1"/>
+    <col min="3" max="3" width="55.7265625" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" customWidth="1"/>
+    <col min="6" max="6" width="21.26953125" customWidth="1"/>
+    <col min="7" max="7" width="18.54296875" style="17" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="43.42578125" customWidth="1"/>
+    <col min="9" max="9" width="43.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="40"/>
-    </row>
-    <row r="2" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="43"/>
-    </row>
-    <row r="4" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="46"/>
-    </row>
-    <row r="5" spans="1:9" ht="55.5" customHeight="1">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
+    </row>
+    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="45"/>
+    </row>
+    <row r="5" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -3749,7 +3792,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="47.25" customHeight="1">
+    <row r="6" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -3776,7 +3819,7 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:9" ht="47.25" customHeight="1">
+    <row r="7" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -3803,7 +3846,7 @@
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9" ht="47.25" customHeight="1">
+    <row r="8" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -3830,7 +3873,7 @@
       </c>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="47.25" customHeight="1">
+    <row r="9" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -3857,7 +3900,7 @@
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="10" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -3884,7 +3927,7 @@
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="11" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -3911,7 +3954,7 @@
       </c>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="12" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -3938,7 +3981,7 @@
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="13" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -3965,7 +4008,7 @@
       </c>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="14" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -3992,7 +4035,7 @@
       </c>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="15" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -4019,7 +4062,7 @@
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="16" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -4044,7 +4087,7 @@
       </c>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="17" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -4071,7 +4114,7 @@
       </c>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="18" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -4100,7 +4143,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="19" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>14</v>
       </c>
@@ -4129,7 +4172,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="20" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>15</v>
       </c>
@@ -4158,34 +4201,34 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
-      <c r="A21" s="22">
+    <row r="21" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="21">
         <v>16</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="22">
         <v>196870802</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="26">
-        <v>1</v>
-      </c>
-      <c r="F21" s="27">
+      <c r="E21" s="25">
+        <v>1</v>
+      </c>
+      <c r="F21" s="26">
         <v>46237</v>
       </c>
-      <c r="G21" s="28"/>
-      <c r="H21" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="21" t="s">
+      <c r="G21" s="27"/>
+      <c r="H21" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="22" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>17</v>
       </c>
@@ -4212,7 +4255,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="23" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>18</v>
       </c>
@@ -4239,7 +4282,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="24" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>19</v>
       </c>
@@ -4266,7 +4309,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="25" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>20</v>
       </c>
@@ -4293,7 +4336,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="26" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>21</v>
       </c>
@@ -4320,7 +4363,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="27" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>22</v>
       </c>
@@ -4347,7 +4390,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="28" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>23</v>
       </c>
@@ -4374,7 +4417,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="29" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>24</v>
       </c>
@@ -4403,7 +4446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="30" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>25</v>
       </c>
@@ -4430,7 +4473,7 @@
       </c>
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="31" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>26</v>
       </c>
@@ -4459,7 +4502,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="32" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>27</v>
       </c>
@@ -4488,7 +4531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="33" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>28</v>
       </c>
@@ -4515,7 +4558,7 @@
       </c>
       <c r="I33" s="9"/>
     </row>
-    <row r="34" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="34" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>29</v>
       </c>
@@ -4544,7 +4587,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="35" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>30</v>
       </c>
@@ -4573,7 +4616,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="36" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>31</v>
       </c>
@@ -4602,7 +4645,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="37" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>32</v>
       </c>
@@ -4631,7 +4674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="38" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>33</v>
       </c>
@@ -4660,11 +4703,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="39" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>34</v>
       </c>
-      <c r="B39" s="34">
+      <c r="B39" s="33">
         <v>180321202</v>
       </c>
       <c r="C39" s="4" t="s">
@@ -4689,7 +4732,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="40" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>35</v>
       </c>
@@ -4718,7 +4761,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="41" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>36</v>
       </c>
@@ -4747,7 +4790,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="42" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>37</v>
       </c>
@@ -4776,7 +4819,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="43" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>38</v>
       </c>
@@ -4805,7 +4848,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="20" customFormat="1" ht="52.5" customHeight="1">
+    <row r="44" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>39</v>
       </c>
@@ -4834,7 +4877,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="45" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>40</v>
       </c>
@@ -4863,7 +4906,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="46" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>41</v>
       </c>
@@ -4892,7 +4935,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="47" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10">
         <v>42</v>
       </c>
@@ -4921,7 +4964,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="48" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10">
         <v>43</v>
       </c>
@@ -4948,7 +4991,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="49" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>44</v>
       </c>
@@ -4968,7 +5011,7 @@
       <c r="I49" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I5"/>
+  <autoFilter ref="A5:I5" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I4"/>
   </mergeCells>
@@ -4979,68 +5022,68 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="55.7109375" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" style="17" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" customWidth="1"/>
+    <col min="3" max="3" width="55.7265625" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" customWidth="1"/>
+    <col min="6" max="6" width="21.26953125" customWidth="1"/>
+    <col min="7" max="7" width="18.54296875" style="17" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="43.42578125" customWidth="1"/>
+    <col min="9" max="9" width="43.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="40"/>
-    </row>
-    <row r="2" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="43"/>
-    </row>
-    <row r="4" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="46"/>
-    </row>
-    <row r="5" spans="1:9" ht="55.5" customHeight="1">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
+    </row>
+    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="45"/>
+    </row>
+    <row r="5" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -5069,7 +5112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="47.25" customHeight="1">
+    <row r="6" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -5096,7 +5139,7 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:9" ht="47.25" customHeight="1">
+    <row r="7" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -5123,7 +5166,7 @@
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9" ht="47.25" customHeight="1">
+    <row r="8" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -5150,7 +5193,7 @@
       </c>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="47.25" customHeight="1">
+    <row r="9" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -5177,7 +5220,7 @@
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="10" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -5204,7 +5247,7 @@
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="11" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -5231,7 +5274,7 @@
       </c>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="12" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -5258,11 +5301,11 @@
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="13" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>8</v>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="33">
         <v>180321202</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -5285,7 +5328,7 @@
       </c>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="14" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -5312,7 +5355,7 @@
       </c>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="15" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -5339,7 +5382,7 @@
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="16" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -5366,7 +5409,7 @@
       </c>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="17" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -5393,7 +5436,7 @@
       </c>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="18" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -5420,7 +5463,7 @@
       </c>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="19" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -5447,7 +5490,7 @@
       </c>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="20" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -5474,7 +5517,7 @@
       </c>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="21" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>16</v>
       </c>
@@ -5501,7 +5544,7 @@
       </c>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="22" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>17</v>
       </c>
@@ -5528,7 +5571,7 @@
       </c>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="23" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>18</v>
       </c>
@@ -5557,7 +5600,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="24" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>19</v>
       </c>
@@ -5586,7 +5629,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="25" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>20</v>
       </c>
@@ -5615,7 +5658,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="26" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>21</v>
       </c>
@@ -5644,7 +5687,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="27" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>22</v>
       </c>
@@ -5671,7 +5714,7 @@
       </c>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="28" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>23</v>
       </c>
@@ -5694,7 +5737,7 @@
       </c>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="29" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>24</v>
       </c>
@@ -5721,7 +5764,7 @@
       </c>
       <c r="I29" s="9"/>
     </row>
-    <row r="30" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="30" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>25</v>
       </c>
@@ -5750,7 +5793,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="31" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>26</v>
       </c>
@@ -5769,7 +5812,7 @@
       <c r="F31" s="7">
         <v>46238</v>
       </c>
-      <c r="G31" s="28" t="s">
+      <c r="G31" s="27" t="s">
         <v>128</v>
       </c>
       <c r="H31" s="6" t="s">
@@ -5779,7 +5822,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="32" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>27</v>
       </c>
@@ -5808,7 +5851,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="33" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>28</v>
       </c>
@@ -5837,65 +5880,65 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
-      <c r="A34" s="22">
+    <row r="34" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="21">
         <v>29</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="22">
         <v>196870702</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="D34" s="25" t="s">
+      <c r="D34" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E34" s="26">
-        <v>1</v>
-      </c>
-      <c r="F34" s="27">
+      <c r="E34" s="25">
+        <v>1</v>
+      </c>
+      <c r="F34" s="26">
         <v>46238</v>
       </c>
-      <c r="G34" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H34" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" s="21" t="s">
+      <c r="G34" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
-      <c r="A35" s="22">
+    <row r="35" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="21">
         <v>30</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B35" s="22">
         <v>196870802</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="D35" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E35" s="26">
-        <v>1</v>
-      </c>
-      <c r="F35" s="27">
+      <c r="E35" s="25">
+        <v>1</v>
+      </c>
+      <c r="F35" s="26">
         <v>46238</v>
       </c>
-      <c r="G35" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H35" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I35" s="21" t="s">
+      <c r="G35" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="36" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>31</v>
       </c>
@@ -5905,7 +5948,7 @@
       <c r="C36" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D36" s="36" t="s">
+      <c r="D36" s="35" t="s">
         <v>126</v>
       </c>
       <c r="E36" s="13">
@@ -5920,7 +5963,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="37" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>32</v>
       </c>
@@ -5930,7 +5973,7 @@
       <c r="C37" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D37" s="36" t="s">
+      <c r="D37" s="35" t="s">
         <v>126</v>
       </c>
       <c r="E37" s="13">
@@ -5945,7 +5988,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="38" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>33</v>
       </c>
@@ -5955,7 +5998,7 @@
       <c r="C38" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D38" s="36" t="s">
+      <c r="D38" s="35" t="s">
         <v>126</v>
       </c>
       <c r="E38" s="13">
@@ -5970,7 +6013,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="39" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>34</v>
       </c>
@@ -5980,7 +6023,7 @@
       <c r="C39" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D39" s="36" t="s">
+      <c r="D39" s="35" t="s">
         <v>126</v>
       </c>
       <c r="E39" s="13">
@@ -5995,7 +6038,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="40" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <v>35</v>
       </c>
@@ -6005,7 +6048,7 @@
       <c r="C40" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="35" t="s">
         <v>126</v>
       </c>
       <c r="E40" s="13">
@@ -6020,7 +6063,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="41" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10">
         <v>36</v>
       </c>
@@ -6030,7 +6073,7 @@
       <c r="C41" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D41" s="36" t="s">
+      <c r="D41" s="35" t="s">
         <v>126</v>
       </c>
       <c r="E41" s="13">
@@ -6045,7 +6088,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="42" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <v>37</v>
       </c>
@@ -6055,7 +6098,7 @@
       <c r="C42" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D42" s="36" t="s">
+      <c r="D42" s="35" t="s">
         <v>126</v>
       </c>
       <c r="E42" s="13">
@@ -6074,7 +6117,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="43" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>38</v>
       </c>
@@ -6084,7 +6127,7 @@
       <c r="C43" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D43" s="35" t="s">
+      <c r="D43" s="34" t="s">
         <v>126</v>
       </c>
       <c r="E43" s="6">
@@ -6103,7 +6146,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="20" customFormat="1" ht="52.5" customHeight="1">
+    <row r="44" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>39</v>
       </c>
@@ -6113,7 +6156,7 @@
       <c r="C44" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D44" s="35" t="s">
+      <c r="D44" s="34" t="s">
         <v>126</v>
       </c>
       <c r="E44" s="6">
@@ -6132,7 +6175,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="45" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>40</v>
       </c>
@@ -6142,7 +6185,7 @@
       <c r="C45" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D45" s="35" t="s">
+      <c r="D45" s="34" t="s">
         <v>126</v>
       </c>
       <c r="E45" s="6">
@@ -6161,7 +6204,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="46" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>41</v>
       </c>
@@ -6171,7 +6214,7 @@
       <c r="C46" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D46" s="35" t="s">
+      <c r="D46" s="34" t="s">
         <v>126</v>
       </c>
       <c r="E46" s="6">
@@ -6190,7 +6233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="47" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>42</v>
       </c>
@@ -6200,7 +6243,7 @@
       <c r="C47" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D47" s="35" t="s">
+      <c r="D47" s="34" t="s">
         <v>126</v>
       </c>
       <c r="E47" s="6">
@@ -6219,7 +6262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="48" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>43</v>
       </c>
@@ -6229,7 +6272,7 @@
       <c r="C48" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D48" s="35" t="s">
+      <c r="D48" s="34" t="s">
         <v>126</v>
       </c>
       <c r="E48" s="6">
@@ -6248,7 +6291,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="49" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>44</v>
       </c>
@@ -6258,7 +6301,7 @@
       <c r="C49" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D49" s="35" t="s">
+      <c r="D49" s="34" t="s">
         <v>126</v>
       </c>
       <c r="E49" s="6">
@@ -6277,7 +6320,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="50" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>45</v>
       </c>
@@ -6287,7 +6330,7 @@
       <c r="C50" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D50" s="35" t="s">
+      <c r="D50" s="34" t="s">
         <v>126</v>
       </c>
       <c r="E50" s="6">
@@ -6306,7 +6349,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="51" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>46</v>
       </c>
@@ -6316,7 +6359,7 @@
       <c r="C51" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D51" s="35" t="s">
+      <c r="D51" s="34" t="s">
         <v>126</v>
       </c>
       <c r="E51" s="6">
@@ -6335,7 +6378,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="52" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>47</v>
       </c>
@@ -6345,7 +6388,7 @@
       <c r="C52" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D52" s="35" t="s">
+      <c r="D52" s="34" t="s">
         <v>126</v>
       </c>
       <c r="E52" s="6">
@@ -6364,13 +6407,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="53" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>48</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="35" t="s">
+      <c r="D53" s="34" t="s">
         <v>126</v>
       </c>
       <c r="E53" s="6"/>
@@ -6384,7 +6427,7 @@
       <c r="I53" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I5"/>
+  <autoFilter ref="A5:I5" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I4"/>
   </mergeCells>
@@ -6395,68 +6438,68 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="55.7109375" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" style="17" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" customWidth="1"/>
+    <col min="3" max="3" width="55.7265625" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" customWidth="1"/>
+    <col min="6" max="6" width="21.26953125" customWidth="1"/>
+    <col min="7" max="7" width="18.54296875" style="17" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="43.42578125" customWidth="1"/>
+    <col min="9" max="9" width="43.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="40"/>
-    </row>
-    <row r="2" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="43"/>
-    </row>
-    <row r="4" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="46"/>
-    </row>
-    <row r="5" spans="1:9" ht="55.5" customHeight="1">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
+    </row>
+    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="45"/>
+    </row>
+    <row r="5" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -6485,7 +6528,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="47.25" customHeight="1">
+    <row r="6" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -6495,7 +6538,7 @@
       <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E6" s="6">
@@ -6512,7 +6555,7 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:9" ht="47.25" customHeight="1">
+    <row r="7" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -6522,7 +6565,7 @@
       <c r="C7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E7" s="6">
@@ -6539,7 +6582,7 @@
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9" ht="47.25" customHeight="1">
+    <row r="8" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -6549,7 +6592,7 @@
       <c r="C8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E8" s="6">
@@ -6566,7 +6609,7 @@
       </c>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="47.25" customHeight="1">
+    <row r="9" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -6576,7 +6619,7 @@
       <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E9" s="6">
@@ -6593,7 +6636,7 @@
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="10" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -6603,7 +6646,7 @@
       <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E10" s="6">
@@ -6620,7 +6663,7 @@
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="11" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -6630,7 +6673,7 @@
       <c r="C11" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E11" s="6">
@@ -6647,7 +6690,7 @@
       </c>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="12" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -6657,7 +6700,7 @@
       <c r="C12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E12" s="6">
@@ -6674,7 +6717,7 @@
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="13" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -6684,7 +6727,7 @@
       <c r="C13" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E13" s="6">
@@ -6701,7 +6744,7 @@
       </c>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="14" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -6711,7 +6754,7 @@
       <c r="C14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E14" s="6">
@@ -6728,7 +6771,7 @@
       </c>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="15" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -6738,7 +6781,7 @@
       <c r="C15" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E15" s="6">
@@ -6755,7 +6798,7 @@
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="16" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -6765,7 +6808,7 @@
       <c r="C16" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E16" s="6">
@@ -6782,7 +6825,7 @@
       </c>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="17" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -6792,7 +6835,7 @@
       <c r="C17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E17" s="6">
@@ -6809,7 +6852,7 @@
       </c>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="18" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -6819,7 +6862,7 @@
       <c r="C18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E18" s="6">
@@ -6836,7 +6879,7 @@
       </c>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="19" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -6846,7 +6889,7 @@
       <c r="C19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E19" s="6">
@@ -6863,7 +6906,7 @@
       </c>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="20" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -6873,7 +6916,7 @@
       <c r="C20" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E20" s="6">
@@ -6890,7 +6933,7 @@
       </c>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="21" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>16</v>
       </c>
@@ -6900,7 +6943,7 @@
       <c r="C21" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E21" s="6">
@@ -6917,7 +6960,7 @@
       </c>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="22" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>17</v>
       </c>
@@ -6927,7 +6970,7 @@
       <c r="C22" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E22" s="6">
@@ -6944,7 +6987,7 @@
       </c>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="23" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>18</v>
       </c>
@@ -6954,7 +6997,7 @@
       <c r="C23" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D23" s="35" t="s">
+      <c r="D23" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E23" s="6">
@@ -6971,7 +7014,7 @@
       </c>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="24" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>19</v>
       </c>
@@ -6981,7 +7024,7 @@
       <c r="C24" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="35" t="s">
+      <c r="D24" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E24" s="6">
@@ -6998,7 +7041,7 @@
       </c>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="25" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>20</v>
       </c>
@@ -7008,7 +7051,7 @@
       <c r="C25" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="35" t="s">
+      <c r="D25" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E25" s="6">
@@ -7025,7 +7068,7 @@
       </c>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="26" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>21</v>
       </c>
@@ -7035,7 +7078,7 @@
       <c r="C26" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D26" s="35" t="s">
+      <c r="D26" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E26" s="6">
@@ -7054,7 +7097,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="27" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>22</v>
       </c>
@@ -7064,7 +7107,7 @@
       <c r="C27" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D27" s="35" t="s">
+      <c r="D27" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E27" s="6">
@@ -7083,7 +7126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="28" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>23</v>
       </c>
@@ -7093,7 +7136,7 @@
       <c r="C28" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="35" t="s">
+      <c r="D28" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E28" s="6">
@@ -7112,7 +7155,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="29" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>24</v>
       </c>
@@ -7122,7 +7165,7 @@
       <c r="C29" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D29" s="35" t="s">
+      <c r="D29" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E29" s="6">
@@ -7139,7 +7182,7 @@
       </c>
       <c r="I29" s="9"/>
     </row>
-    <row r="30" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="30" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>25</v>
       </c>
@@ -7149,7 +7192,7 @@
       <c r="C30" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="35" t="s">
+      <c r="D30" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E30" s="6">
@@ -7168,7 +7211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="31" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>26</v>
       </c>
@@ -7178,7 +7221,7 @@
       <c r="C31" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="35" t="s">
+      <c r="D31" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E31" s="6">
@@ -7197,7 +7240,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="32" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>27</v>
       </c>
@@ -7207,7 +7250,7 @@
       <c r="C32" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D32" s="35" t="s">
+      <c r="D32" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E32" s="6">
@@ -7226,7 +7269,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="33" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>28</v>
       </c>
@@ -7236,7 +7279,7 @@
       <c r="C33" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D33" s="35" t="s">
+      <c r="D33" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E33" s="6">
@@ -7255,7 +7298,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="34" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>29</v>
       </c>
@@ -7265,7 +7308,7 @@
       <c r="C34" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="35" t="s">
+      <c r="D34" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E34" s="6">
@@ -7284,7 +7327,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="35" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>30</v>
       </c>
@@ -7294,7 +7337,7 @@
       <c r="C35" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E35" s="6">
@@ -7311,7 +7354,7 @@
       </c>
       <c r="I35" s="9"/>
     </row>
-    <row r="36" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="36" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>31</v>
       </c>
@@ -7321,7 +7364,7 @@
       <c r="C36" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="35" t="s">
+      <c r="D36" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E36" s="6">
@@ -7338,7 +7381,7 @@
       </c>
       <c r="I36" s="9"/>
     </row>
-    <row r="37" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="37" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>32</v>
       </c>
@@ -7348,7 +7391,7 @@
       <c r="C37" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D37" s="36" t="s">
+      <c r="D37" s="35" t="s">
         <v>133</v>
       </c>
       <c r="E37" s="13">
@@ -7367,7 +7410,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="38" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>33</v>
       </c>
@@ -7377,7 +7420,7 @@
       <c r="C38" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="36" t="s">
+      <c r="D38" s="35" t="s">
         <v>133</v>
       </c>
       <c r="E38" s="13">
@@ -7394,7 +7437,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="39" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>34</v>
       </c>
@@ -7404,7 +7447,7 @@
       <c r="C39" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D39" s="36" t="s">
+      <c r="D39" s="35" t="s">
         <v>133</v>
       </c>
       <c r="E39" s="13">
@@ -7423,7 +7466,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="40" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>35</v>
       </c>
@@ -7433,7 +7476,7 @@
       <c r="C40" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D40" s="35" t="s">
+      <c r="D40" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E40" s="6">
@@ -7452,7 +7495,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="41" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>36</v>
       </c>
@@ -7462,7 +7505,7 @@
       <c r="C41" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D41" s="35" t="s">
+      <c r="D41" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E41" s="6">
@@ -7481,7 +7524,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="42" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>37</v>
       </c>
@@ -7491,7 +7534,7 @@
       <c r="C42" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D42" s="35" t="s">
+      <c r="D42" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E42" s="6">
@@ -7510,7 +7553,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="43" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>38</v>
       </c>
@@ -7520,7 +7563,7 @@
       <c r="C43" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D43" s="35" t="s">
+      <c r="D43" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E43" s="6">
@@ -7539,7 +7582,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="20" customFormat="1" ht="52.5" customHeight="1">
+    <row r="44" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>39</v>
       </c>
@@ -7549,7 +7592,7 @@
       <c r="C44" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D44" s="35" t="s">
+      <c r="D44" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E44" s="6">
@@ -7568,7 +7611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="45" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>40</v>
       </c>
@@ -7578,7 +7621,7 @@
       <c r="C45" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D45" s="35" t="s">
+      <c r="D45" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E45" s="6">
@@ -7597,7 +7640,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="46" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>41</v>
       </c>
@@ -7607,7 +7650,7 @@
       <c r="C46" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D46" s="35" t="s">
+      <c r="D46" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E46" s="6">
@@ -7626,7 +7669,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="47" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10">
         <v>42</v>
       </c>
@@ -7636,7 +7679,7 @@
       <c r="C47" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D47" s="36" t="s">
+      <c r="D47" s="35" t="s">
         <v>133</v>
       </c>
       <c r="E47" s="13">
@@ -7653,36 +7696,36 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
-      <c r="A48" s="22">
+    <row r="48" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="21">
         <v>43</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B48" s="22">
         <v>196870702</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="D48" s="37" t="s">
+      <c r="D48" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E48" s="26">
-        <v>1</v>
-      </c>
-      <c r="F48" s="27">
+      <c r="E48" s="25">
+        <v>1</v>
+      </c>
+      <c r="F48" s="26">
         <v>46239</v>
       </c>
-      <c r="G48" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H48" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I48" s="21" t="s">
+      <c r="G48" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H48" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="49" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10">
         <v>44</v>
       </c>
@@ -7692,7 +7735,7 @@
       <c r="C49" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D49" s="36" t="s">
+      <c r="D49" s="35" t="s">
         <v>133</v>
       </c>
       <c r="E49" s="13">
@@ -7709,7 +7752,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="50" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10">
         <v>45</v>
       </c>
@@ -7719,7 +7762,7 @@
       <c r="C50" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D50" s="36" t="s">
+      <c r="D50" s="35" t="s">
         <v>133</v>
       </c>
       <c r="E50" s="13">
@@ -7736,7 +7779,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="51" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10">
         <v>46</v>
       </c>
@@ -7746,7 +7789,7 @@
       <c r="C51" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D51" s="36" t="s">
+      <c r="D51" s="35" t="s">
         <v>133</v>
       </c>
       <c r="E51" s="13">
@@ -7763,7 +7806,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="52" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10">
         <v>47</v>
       </c>
@@ -7773,7 +7816,7 @@
       <c r="C52" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="36" t="s">
+      <c r="D52" s="35" t="s">
         <v>133</v>
       </c>
       <c r="E52" s="13">
@@ -7790,13 +7833,13 @@
         <v>118</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="53" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>48</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="35" t="s">
+      <c r="D53" s="34" t="s">
         <v>133</v>
       </c>
       <c r="E53" s="6"/>
@@ -7810,7 +7853,7 @@
       <c r="I53" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I5"/>
+  <autoFilter ref="A5:I5" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I4"/>
   </mergeCells>
@@ -7821,68 +7864,68 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I59"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="55.7109375" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" style="17" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" customWidth="1"/>
+    <col min="3" max="3" width="55.7265625" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" customWidth="1"/>
+    <col min="6" max="6" width="21.26953125" customWidth="1"/>
+    <col min="7" max="7" width="18.54296875" style="17" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="43.42578125" customWidth="1"/>
+    <col min="9" max="9" width="43.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="40"/>
-    </row>
-    <row r="2" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="43"/>
-    </row>
-    <row r="4" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="46"/>
-    </row>
-    <row r="5" spans="1:9" ht="55.5" customHeight="1">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
+    </row>
+    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="45"/>
+    </row>
+    <row r="5" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -7911,7 +7954,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="47.25" customHeight="1">
+    <row r="6" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -7921,7 +7964,7 @@
       <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E6" s="6">
@@ -7938,7 +7981,7 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:9" ht="47.25" customHeight="1">
+    <row r="7" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -7948,7 +7991,7 @@
       <c r="C7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E7" s="6">
@@ -7965,7 +8008,7 @@
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9" ht="47.25" customHeight="1">
+    <row r="8" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -7975,7 +8018,7 @@
       <c r="C8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E8" s="6">
@@ -7992,7 +8035,7 @@
       </c>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="47.25" customHeight="1">
+    <row r="9" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -8002,7 +8045,7 @@
       <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E9" s="6">
@@ -8019,7 +8062,7 @@
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="10" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -8029,7 +8072,7 @@
       <c r="C10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E10" s="6">
@@ -8046,7 +8089,7 @@
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="11" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -8056,7 +8099,7 @@
       <c r="C11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E11" s="6">
@@ -8071,7 +8114,7 @@
       </c>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="12" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -8081,7 +8124,7 @@
       <c r="C12" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E12" s="6">
@@ -8098,7 +8141,7 @@
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="13" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -8108,7 +8151,7 @@
       <c r="C13" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E13" s="6">
@@ -8125,7 +8168,7 @@
       </c>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="14" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -8135,7 +8178,7 @@
       <c r="C14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E14" s="6">
@@ -8152,7 +8195,7 @@
       </c>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="15" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -8162,7 +8205,7 @@
       <c r="C15" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E15" s="6">
@@ -8179,7 +8222,7 @@
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="16" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -8189,7 +8232,7 @@
       <c r="C16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E16" s="6">
@@ -8206,7 +8249,7 @@
       </c>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="17" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -8216,7 +8259,7 @@
       <c r="C17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E17" s="6">
@@ -8233,7 +8276,7 @@
       </c>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="18" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -8243,7 +8286,7 @@
       <c r="C18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E18" s="6">
@@ -8260,7 +8303,7 @@
       </c>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="19" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -8270,7 +8313,7 @@
       <c r="C19" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E19" s="6">
@@ -8287,7 +8330,7 @@
       </c>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="20" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -8297,7 +8340,7 @@
       <c r="C20" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E20" s="6">
@@ -8314,7 +8357,7 @@
       </c>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="21" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>16</v>
       </c>
@@ -8324,7 +8367,7 @@
       <c r="C21" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E21" s="6">
@@ -8341,7 +8384,7 @@
       </c>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="22" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>17</v>
       </c>
@@ -8351,7 +8394,7 @@
       <c r="C22" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E22" s="6">
@@ -8368,7 +8411,7 @@
       </c>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="23" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>18</v>
       </c>
@@ -8378,7 +8421,7 @@
       <c r="C23" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="35" t="s">
+      <c r="D23" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E23" s="6">
@@ -8395,7 +8438,7 @@
       </c>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="24" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>19</v>
       </c>
@@ -8405,7 +8448,7 @@
       <c r="C24" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="35" t="s">
+      <c r="D24" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E24" s="6">
@@ -8422,7 +8465,7 @@
       </c>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="25" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>20</v>
       </c>
@@ -8432,7 +8475,7 @@
       <c r="C25" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D25" s="35" t="s">
+      <c r="D25" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E25" s="6">
@@ -8449,7 +8492,7 @@
       </c>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="26" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>21</v>
       </c>
@@ -8459,7 +8502,7 @@
       <c r="C26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="35" t="s">
+      <c r="D26" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E26" s="6">
@@ -8476,7 +8519,7 @@
       </c>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="27" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>22</v>
       </c>
@@ -8486,7 +8529,7 @@
       <c r="C27" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="36" t="s">
+      <c r="D27" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E27" s="13">
@@ -8503,36 +8546,36 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
-      <c r="A28" s="22">
+    <row r="28" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="21">
         <v>23</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B28" s="22">
         <v>196870702</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="E28" s="26">
-        <v>1</v>
-      </c>
-      <c r="F28" s="27">
+      <c r="E28" s="25">
+        <v>1</v>
+      </c>
+      <c r="F28" s="26">
         <v>46240</v>
       </c>
-      <c r="G28" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H28" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I28" s="21" t="s">
+      <c r="G28" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="29" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>24</v>
       </c>
@@ -8542,7 +8585,7 @@
       <c r="C29" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E29" s="13">
@@ -8559,7 +8602,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="30" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>25</v>
       </c>
@@ -8569,7 +8612,7 @@
       <c r="C30" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="36" t="s">
+      <c r="D30" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E30" s="13">
@@ -8586,7 +8629,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="31" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>26</v>
       </c>
@@ -8596,7 +8639,7 @@
       <c r="C31" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E31" s="13">
@@ -8613,7 +8656,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="32" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>27</v>
       </c>
@@ -8623,7 +8666,7 @@
       <c r="C32" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="36" t="s">
+      <c r="D32" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E32" s="13">
@@ -8640,7 +8683,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="33" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>28</v>
       </c>
@@ -8650,7 +8693,7 @@
       <c r="C33" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E33" s="13">
@@ -8667,7 +8710,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="34" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>29</v>
       </c>
@@ -8677,7 +8720,7 @@
       <c r="C34" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="36" t="s">
+      <c r="D34" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E34" s="13">
@@ -8694,7 +8737,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="35" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <v>30</v>
       </c>
@@ -8704,7 +8747,7 @@
       <c r="C35" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D35" s="36" t="s">
+      <c r="D35" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E35" s="13">
@@ -8721,7 +8764,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="36" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>31</v>
       </c>
@@ -8731,7 +8774,7 @@
       <c r="C36" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="36" t="s">
+      <c r="D36" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E36" s="13">
@@ -8748,7 +8791,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="37" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>32</v>
       </c>
@@ -8758,7 +8801,7 @@
       <c r="C37" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="35" t="s">
+      <c r="D37" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E37" s="6">
@@ -8775,7 +8818,7 @@
       </c>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="38" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>33</v>
       </c>
@@ -8785,7 +8828,7 @@
       <c r="C38" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D38" s="35" t="s">
+      <c r="D38" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E38" s="6">
@@ -8802,7 +8845,7 @@
       </c>
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="39" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>34</v>
       </c>
@@ -8812,7 +8855,7 @@
       <c r="C39" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="35" t="s">
+      <c r="D39" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E39" s="6">
@@ -8829,7 +8872,7 @@
       </c>
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="40" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <v>35</v>
       </c>
@@ -8839,7 +8882,7 @@
       <c r="C40" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E40" s="13">
@@ -8858,7 +8901,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="41" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>36</v>
       </c>
@@ -8868,7 +8911,7 @@
       <c r="C41" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D41" s="35" t="s">
+      <c r="D41" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E41" s="6">
@@ -8887,7 +8930,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="42" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>37</v>
       </c>
@@ -8897,7 +8940,7 @@
       <c r="C42" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D42" s="35" t="s">
+      <c r="D42" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E42" s="6">
@@ -8916,7 +8959,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="43" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10">
         <v>38</v>
       </c>
@@ -8926,7 +8969,7 @@
       <c r="C43" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E43" s="13">
@@ -8943,7 +8986,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="20" customFormat="1" ht="52.5" customHeight="1">
+    <row r="44" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>39</v>
       </c>
@@ -8953,7 +8996,7 @@
       <c r="C44" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D44" s="35" t="s">
+      <c r="D44" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E44" s="6">
@@ -8972,7 +9015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="45" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>40</v>
       </c>
@@ -8982,7 +9025,7 @@
       <c r="C45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D45" s="35" t="s">
+      <c r="D45" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E45" s="6">
@@ -9001,7 +9044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="46" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>41</v>
       </c>
@@ -9011,7 +9054,7 @@
       <c r="C46" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D46" s="35" t="s">
+      <c r="D46" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E46" s="6">
@@ -9030,7 +9073,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="47" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>42</v>
       </c>
@@ -9040,7 +9083,7 @@
       <c r="C47" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D47" s="35" t="s">
+      <c r="D47" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E47" s="6">
@@ -9059,7 +9102,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="48" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>43</v>
       </c>
@@ -9069,7 +9112,7 @@
       <c r="C48" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="35" t="s">
+      <c r="D48" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E48" s="6">
@@ -9088,17 +9131,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="49" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>44</v>
       </c>
       <c r="B49" s="19">
         <v>170108801</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="D49" s="35" t="s">
+      <c r="D49" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E49" s="6">
@@ -9117,7 +9160,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="50" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10">
         <v>45</v>
       </c>
@@ -9127,7 +9170,7 @@
       <c r="C50" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D50" s="36" t="s">
+      <c r="D50" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E50" s="13">
@@ -9144,7 +9187,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="51" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10">
         <v>46</v>
       </c>
@@ -9154,7 +9197,7 @@
       <c r="C51" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="D51" s="36" t="s">
+      <c r="D51" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E51" s="13">
@@ -9173,7 +9216,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="52" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10">
         <v>47</v>
       </c>
@@ -9183,7 +9226,7 @@
       <c r="C52" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D52" s="36" t="s">
+      <c r="D52" s="35" t="s">
         <v>138</v>
       </c>
       <c r="E52" s="13">
@@ -9202,7 +9245,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="53" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>48</v>
       </c>
@@ -9212,7 +9255,7 @@
       <c r="C53" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D53" s="35" t="s">
+      <c r="D53" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E53" s="6">
@@ -9231,7 +9274,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="54" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>49</v>
       </c>
@@ -9241,7 +9284,7 @@
       <c r="C54" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D54" s="35" t="s">
+      <c r="D54" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E54" s="6">
@@ -9260,7 +9303,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="55" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>50</v>
       </c>
@@ -9270,7 +9313,7 @@
       <c r="C55" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D55" s="35" t="s">
+      <c r="D55" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E55" s="6">
@@ -9289,7 +9332,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="56" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>51</v>
       </c>
@@ -9299,7 +9342,7 @@
       <c r="C56" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D56" s="35" t="s">
+      <c r="D56" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E56" s="6">
@@ -9318,7 +9361,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="57" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>52</v>
       </c>
@@ -9328,7 +9371,7 @@
       <c r="C57" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D57" s="35" t="s">
+      <c r="D57" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E57" s="6">
@@ -9347,42 +9390,42 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
-      <c r="A58" s="22">
+    <row r="58" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="21">
         <v>53</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B58" s="22">
         <v>196870501</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C58" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="D58" s="37" t="s">
+      <c r="D58" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="E58" s="26">
-        <v>1</v>
-      </c>
-      <c r="F58" s="27">
+      <c r="E58" s="25">
+        <v>1</v>
+      </c>
+      <c r="F58" s="26">
         <v>46240</v>
       </c>
-      <c r="G58" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H58" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I58" s="21" t="s">
+      <c r="G58" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" s="20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="59" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>54</v>
       </c>
       <c r="B59" s="19"/>
       <c r="C59" s="4"/>
-      <c r="D59" s="35" t="s">
+      <c r="D59" s="34" t="s">
         <v>138</v>
       </c>
       <c r="E59" s="6"/>
@@ -9396,7 +9439,7 @@
       <c r="I59" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I5"/>
+  <autoFilter ref="A5:I5" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I4"/>
   </mergeCells>
@@ -9407,68 +9450,68 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I59"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="55.7109375" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" style="17" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" customWidth="1"/>
+    <col min="3" max="3" width="55.7265625" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" customWidth="1"/>
+    <col min="6" max="6" width="21.26953125" customWidth="1"/>
+    <col min="7" max="7" width="18.54296875" style="17" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="43.42578125" customWidth="1"/>
+    <col min="9" max="9" width="43.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="40"/>
-    </row>
-    <row r="2" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="43"/>
-    </row>
-    <row r="4" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="46"/>
-    </row>
-    <row r="5" spans="1:9" ht="55.5" customHeight="1">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
+    </row>
+    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="45"/>
+    </row>
+    <row r="5" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -9497,7 +9540,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="47.25" customHeight="1">
+    <row r="6" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -9507,7 +9550,7 @@
       <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E6" s="6">
@@ -9524,7 +9567,7 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:9" ht="47.25" customHeight="1">
+    <row r="7" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -9534,7 +9577,7 @@
       <c r="C7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E7" s="6">
@@ -9551,7 +9594,7 @@
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9" ht="47.25" customHeight="1">
+    <row r="8" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -9561,7 +9604,7 @@
       <c r="C8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E8" s="6">
@@ -9578,7 +9621,7 @@
       </c>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="47.25" customHeight="1">
+    <row r="9" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -9588,7 +9631,7 @@
       <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E9" s="6">
@@ -9605,7 +9648,7 @@
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="10" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -9615,7 +9658,7 @@
       <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E10" s="6">
@@ -9632,7 +9675,7 @@
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="11" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -9642,7 +9685,7 @@
       <c r="C11" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E11" s="6">
@@ -9659,17 +9702,17 @@
       </c>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="12" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>7</v>
       </c>
       <c r="B12" s="19">
         <v>170108801</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E12" s="6">
@@ -9686,7 +9729,7 @@
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="13" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -9696,7 +9739,7 @@
       <c r="C13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E13" s="6">
@@ -9713,7 +9756,7 @@
       </c>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="14" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -9723,7 +9766,7 @@
       <c r="C14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E14" s="6">
@@ -9740,7 +9783,7 @@
       </c>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="15" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -9750,7 +9793,7 @@
       <c r="C15" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E15" s="6">
@@ -9767,7 +9810,7 @@
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="16" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -9777,7 +9820,7 @@
       <c r="C16" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E16" s="6">
@@ -9794,7 +9837,7 @@
       </c>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="17" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -9804,7 +9847,7 @@
       <c r="C17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E17" s="6">
@@ -9823,7 +9866,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="18" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -9833,7 +9876,7 @@
       <c r="C18" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E18" s="6">
@@ -9852,7 +9895,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="19" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>14</v>
       </c>
@@ -9862,7 +9905,7 @@
       <c r="C19" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="35" t="s">
         <v>145</v>
       </c>
       <c r="E19" s="13">
@@ -9881,36 +9924,36 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
-      <c r="A20" s="22">
+    <row r="20" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="21">
         <v>15</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="22">
         <v>196870501</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="E20" s="26">
-        <v>1</v>
-      </c>
-      <c r="F20" s="27">
+      <c r="E20" s="25">
+        <v>1</v>
+      </c>
+      <c r="F20" s="26">
         <v>46241</v>
       </c>
-      <c r="G20" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="H20" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I20" s="21" t="s">
+      <c r="G20" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="21" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>16</v>
       </c>
@@ -9920,7 +9963,7 @@
       <c r="C21" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="35" t="s">
         <v>145</v>
       </c>
       <c r="E21" s="13">
@@ -9939,7 +9982,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="22" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>17</v>
       </c>
@@ -9949,7 +9992,7 @@
       <c r="C22" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="35" t="s">
         <v>145</v>
       </c>
       <c r="E22" s="13">
@@ -9968,7 +10011,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="23" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>18</v>
       </c>
@@ -9978,7 +10021,7 @@
       <c r="C23" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="35" t="s">
         <v>145</v>
       </c>
       <c r="E23" s="13">
@@ -9997,7 +10040,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="24" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>19</v>
       </c>
@@ -10007,7 +10050,7 @@
       <c r="C24" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="36" t="s">
+      <c r="D24" s="35" t="s">
         <v>145</v>
       </c>
       <c r="E24" s="13">
@@ -10026,7 +10069,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="25" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>20</v>
       </c>
@@ -10036,7 +10079,7 @@
       <c r="C25" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D25" s="36" t="s">
+      <c r="D25" s="35" t="s">
         <v>145</v>
       </c>
       <c r="E25" s="13">
@@ -10053,7 +10096,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="26" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>21</v>
       </c>
@@ -10063,7 +10106,7 @@
       <c r="C26" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="35" t="s">
+      <c r="D26" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E26" s="6">
@@ -10080,7 +10123,7 @@
       </c>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="27" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>22</v>
       </c>
@@ -10090,7 +10133,7 @@
       <c r="C27" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="35" t="s">
+      <c r="D27" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E27" s="6">
@@ -10107,7 +10150,7 @@
       </c>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="28" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>23</v>
       </c>
@@ -10117,7 +10160,7 @@
       <c r="C28" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D28" s="35" t="s">
+      <c r="D28" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E28" s="6">
@@ -10134,7 +10177,7 @@
       </c>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="29" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>24</v>
       </c>
@@ -10144,7 +10187,7 @@
       <c r="C29" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="35" t="s">
+      <c r="D29" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E29" s="6">
@@ -10161,7 +10204,7 @@
       </c>
       <c r="I29" s="9"/>
     </row>
-    <row r="30" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="30" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>25</v>
       </c>
@@ -10171,7 +10214,7 @@
       <c r="C30" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="35" t="s">
+      <c r="D30" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E30" s="6">
@@ -10188,7 +10231,7 @@
       </c>
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="31" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>26</v>
       </c>
@@ -10198,7 +10241,7 @@
       <c r="C31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="35" t="s">
+      <c r="D31" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E31" s="6">
@@ -10215,13 +10258,13 @@
       </c>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="32" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>27</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="35" t="s">
+      <c r="D32" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E32" s="6"/>
@@ -10234,13 +10277,13 @@
       </c>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="33" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>28</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="35" t="s">
+      <c r="D33" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E33" s="6"/>
@@ -10253,13 +10296,13 @@
       </c>
       <c r="I33" s="9"/>
     </row>
-    <row r="34" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="34" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>29</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="35" t="s">
+      <c r="D34" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E34" s="6"/>
@@ -10272,13 +10315,13 @@
       </c>
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="35" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>30</v>
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E35" s="6"/>
@@ -10291,13 +10334,13 @@
       </c>
       <c r="I35" s="9"/>
     </row>
-    <row r="36" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="36" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>31</v>
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="35" t="s">
+      <c r="D36" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E36" s="6"/>
@@ -10310,13 +10353,13 @@
       </c>
       <c r="I36" s="9"/>
     </row>
-    <row r="37" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="37" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>32</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="35" t="s">
+      <c r="D37" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E37" s="6"/>
@@ -10329,13 +10372,13 @@
       </c>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="38" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>33</v>
       </c>
       <c r="B38" s="19"/>
       <c r="C38" s="4"/>
-      <c r="D38" s="35" t="s">
+      <c r="D38" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E38" s="6"/>
@@ -10348,13 +10391,13 @@
       </c>
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="39" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>34</v>
       </c>
       <c r="B39" s="19"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="35" t="s">
+      <c r="D39" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E39" s="6"/>
@@ -10367,13 +10410,13 @@
       </c>
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="40" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>35</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="35" t="s">
+      <c r="D40" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E40" s="6"/>
@@ -10386,13 +10429,13 @@
       </c>
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="41" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>36</v>
       </c>
       <c r="B41" s="19"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="35" t="s">
+      <c r="D41" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E41" s="6"/>
@@ -10405,13 +10448,13 @@
       </c>
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="42" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>37</v>
       </c>
       <c r="B42" s="19"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="35" t="s">
+      <c r="D42" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E42" s="6"/>
@@ -10424,13 +10467,13 @@
       </c>
       <c r="I42" s="9"/>
     </row>
-    <row r="43" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="43" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>38</v>
       </c>
       <c r="B43" s="19"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="35" t="s">
+      <c r="D43" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E43" s="6"/>
@@ -10443,13 +10486,13 @@
       </c>
       <c r="I43" s="9"/>
     </row>
-    <row r="44" spans="1:9" s="20" customFormat="1" ht="52.5" customHeight="1">
+    <row r="44" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>39</v>
       </c>
       <c r="B44" s="19"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="35" t="s">
+      <c r="D44" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E44" s="6"/>
@@ -10462,13 +10505,13 @@
       </c>
       <c r="I44" s="9"/>
     </row>
-    <row r="45" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="45" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>40</v>
       </c>
       <c r="B45" s="19"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="35" t="s">
+      <c r="D45" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E45" s="6"/>
@@ -10481,13 +10524,13 @@
       </c>
       <c r="I45" s="9"/>
     </row>
-    <row r="46" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="46" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>41</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="4"/>
-      <c r="D46" s="35" t="s">
+      <c r="D46" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E46" s="6"/>
@@ -10500,13 +10543,13 @@
       </c>
       <c r="I46" s="9"/>
     </row>
-    <row r="47" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="47" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>42</v>
       </c>
       <c r="B47" s="19"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="35" t="s">
+      <c r="D47" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E47" s="6"/>
@@ -10519,13 +10562,13 @@
       </c>
       <c r="I47" s="9"/>
     </row>
-    <row r="48" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="48" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>43</v>
       </c>
       <c r="B48" s="19"/>
       <c r="C48" s="4"/>
-      <c r="D48" s="35" t="s">
+      <c r="D48" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E48" s="6"/>
@@ -10538,13 +10581,13 @@
       </c>
       <c r="I48" s="9"/>
     </row>
-    <row r="49" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="49" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>44</v>
       </c>
       <c r="B49" s="19"/>
       <c r="C49" s="4"/>
-      <c r="D49" s="35" t="s">
+      <c r="D49" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E49" s="6"/>
@@ -10557,13 +10600,13 @@
       </c>
       <c r="I49" s="9"/>
     </row>
-    <row r="50" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="50" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>45</v>
       </c>
       <c r="B50" s="19"/>
       <c r="C50" s="4"/>
-      <c r="D50" s="35" t="s">
+      <c r="D50" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E50" s="6"/>
@@ -10576,13 +10619,13 @@
       </c>
       <c r="I50" s="9"/>
     </row>
-    <row r="51" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="51" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>46</v>
       </c>
       <c r="B51" s="19"/>
       <c r="C51" s="4"/>
-      <c r="D51" s="35" t="s">
+      <c r="D51" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E51" s="6"/>
@@ -10595,13 +10638,13 @@
       </c>
       <c r="I51" s="9"/>
     </row>
-    <row r="52" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="52" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>47</v>
       </c>
       <c r="B52" s="19"/>
       <c r="C52" s="4"/>
-      <c r="D52" s="35" t="s">
+      <c r="D52" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E52" s="6"/>
@@ -10614,13 +10657,13 @@
       </c>
       <c r="I52" s="9"/>
     </row>
-    <row r="53" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="53" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>48</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="35" t="s">
+      <c r="D53" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E53" s="6"/>
@@ -10633,13 +10676,13 @@
       </c>
       <c r="I53" s="9"/>
     </row>
-    <row r="54" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="54" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>49</v>
       </c>
       <c r="B54" s="19"/>
       <c r="C54" s="4"/>
-      <c r="D54" s="35" t="s">
+      <c r="D54" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E54" s="6"/>
@@ -10652,13 +10695,13 @@
       </c>
       <c r="I54" s="9"/>
     </row>
-    <row r="55" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="55" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>50</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="4"/>
-      <c r="D55" s="35" t="s">
+      <c r="D55" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E55" s="6"/>
@@ -10671,13 +10714,13 @@
       </c>
       <c r="I55" s="9"/>
     </row>
-    <row r="56" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="56" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>51</v>
       </c>
       <c r="B56" s="19"/>
       <c r="C56" s="4"/>
-      <c r="D56" s="35" t="s">
+      <c r="D56" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E56" s="6"/>
@@ -10690,13 +10733,13 @@
       </c>
       <c r="I56" s="9"/>
     </row>
-    <row r="57" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="57" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>52</v>
       </c>
       <c r="B57" s="19"/>
       <c r="C57" s="4"/>
-      <c r="D57" s="35" t="s">
+      <c r="D57" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E57" s="6"/>
@@ -10709,13 +10752,13 @@
       </c>
       <c r="I57" s="9"/>
     </row>
-    <row r="58" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="58" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <v>53</v>
       </c>
       <c r="B58" s="19"/>
       <c r="C58" s="4"/>
-      <c r="D58" s="35" t="s">
+      <c r="D58" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E58" s="6"/>
@@ -10728,13 +10771,13 @@
       </c>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="1:9" s="20" customFormat="1" ht="50.25" customHeight="1">
+    <row r="59" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>54</v>
       </c>
       <c r="B59" s="19"/>
       <c r="C59" s="4"/>
-      <c r="D59" s="35" t="s">
+      <c r="D59" s="34" t="s">
         <v>145</v>
       </c>
       <c r="E59" s="6"/>
@@ -10748,7 +10791,7 @@
       <c r="I59" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I5"/>
+  <autoFilter ref="A5:I5" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I4"/>
   </mergeCells>
@@ -10759,9 +10802,1351 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:I59"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="45"/>
+    </row>
+    <row r="5" spans="1:9" ht="105" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4">
+        <v>169023401</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4">
+        <v>169023501</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4">
+        <v>166702301</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="9"/>
+    </row>
+    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4">
+        <v>166702401</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>5</v>
+      </c>
+      <c r="B10" s="19">
+        <v>176412000</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="6">
+        <v>4</v>
+      </c>
+      <c r="F10" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>6</v>
+      </c>
+      <c r="B11" s="19">
+        <v>176412101</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E11" s="6">
+        <v>4</v>
+      </c>
+      <c r="F11" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" spans="1:9" ht="175" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>7</v>
+      </c>
+      <c r="B12" s="19">
+        <v>170108801</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2</v>
+      </c>
+      <c r="F12" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="9"/>
+    </row>
+    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>8</v>
+      </c>
+      <c r="B13" s="19">
+        <v>192456700</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E13" s="6">
+        <v>4</v>
+      </c>
+      <c r="F13" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>9</v>
+      </c>
+      <c r="B14" s="19">
+        <v>179340302</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2</v>
+      </c>
+      <c r="F14" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="9"/>
+    </row>
+    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>10</v>
+      </c>
+      <c r="B15" s="19">
+        <v>157211601</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="6">
+        <v>4</v>
+      </c>
+      <c r="F15" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>11</v>
+      </c>
+      <c r="B16" s="19">
+        <v>181010400</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2</v>
+      </c>
+      <c r="F16" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="9"/>
+    </row>
+    <row r="17" spans="1:9" ht="126" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>12</v>
+      </c>
+      <c r="B17" s="19">
+        <v>171792001</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" s="6">
+        <v>4</v>
+      </c>
+      <c r="F17" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="126" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>13</v>
+      </c>
+      <c r="B18" s="19">
+        <v>187311900</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="126" x14ac:dyDescent="0.35">
+      <c r="A19" s="10">
+        <v>14</v>
+      </c>
+      <c r="B19" s="18">
+        <v>182962300</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E19" s="13">
+        <v>1</v>
+      </c>
+      <c r="F19" s="14">
+        <v>46241</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="168" x14ac:dyDescent="0.35">
+      <c r="A20" s="21">
+        <v>15</v>
+      </c>
+      <c r="B20" s="22">
+        <v>196870501</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="E20" s="25">
+        <v>1</v>
+      </c>
+      <c r="F20" s="26">
+        <v>46241</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="126" x14ac:dyDescent="0.35">
+      <c r="A21" s="10">
+        <v>16</v>
+      </c>
+      <c r="B21" s="18">
+        <v>182958901</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" s="13">
+        <v>1</v>
+      </c>
+      <c r="F21" s="14">
+        <v>46241</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="126" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
+        <v>17</v>
+      </c>
+      <c r="B22" s="18">
+        <v>182954701</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E22" s="13">
+        <v>1</v>
+      </c>
+      <c r="F22" s="14">
+        <v>46241</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="126" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>18</v>
+      </c>
+      <c r="B23" s="18">
+        <v>189391000</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" s="13">
+        <v>4</v>
+      </c>
+      <c r="F23" s="14">
+        <v>46241</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="168" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>19</v>
+      </c>
+      <c r="B24" s="18">
+        <v>183326500</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" s="13">
+        <v>1</v>
+      </c>
+      <c r="F24" s="14">
+        <v>46241</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="210" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>20</v>
+      </c>
+      <c r="B25" s="18">
+        <v>189672501</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="13">
+        <v>1</v>
+      </c>
+      <c r="F25" s="14">
+        <v>46241</v>
+      </c>
+      <c r="G25" s="16"/>
+      <c r="H25" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A26" s="3">
+        <v>21</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="6">
+        <v>2</v>
+      </c>
+      <c r="F26" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A27" s="3">
+        <v>22</v>
+      </c>
+      <c r="B27" s="19">
+        <v>174617201</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E27" s="6">
+        <v>2</v>
+      </c>
+      <c r="F27" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A28" s="3">
+        <v>23</v>
+      </c>
+      <c r="B28" s="19">
+        <v>182996401</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1</v>
+      </c>
+      <c r="F28" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A29" s="3">
+        <v>24</v>
+      </c>
+      <c r="B29" s="19">
+        <v>176591801</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E29" s="6">
+        <v>4</v>
+      </c>
+      <c r="F29" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A30" s="3">
+        <v>25</v>
+      </c>
+      <c r="B30" s="19">
+        <v>187312501</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1</v>
+      </c>
+      <c r="F30" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A31" s="3">
+        <v>26</v>
+      </c>
+      <c r="B31" s="19">
+        <v>173514801</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1</v>
+      </c>
+      <c r="F31" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A32" s="3">
+        <v>27</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" s="6"/>
+      <c r="F32" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G32" s="8"/>
+      <c r="H32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A33" s="3">
+        <v>28</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G33" s="8"/>
+      <c r="H33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A34" s="3">
+        <v>29</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G34" s="8"/>
+      <c r="H34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A35" s="3">
+        <v>30</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E35" s="6"/>
+      <c r="F35" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G35" s="8"/>
+      <c r="H35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A36" s="3">
+        <v>31</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" s="6"/>
+      <c r="F36" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G36" s="8"/>
+      <c r="H36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A37" s="3">
+        <v>32</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" s="6"/>
+      <c r="F37" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G37" s="8"/>
+      <c r="H37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="9"/>
+    </row>
+    <row r="38" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A38" s="3">
+        <v>33</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" s="6"/>
+      <c r="F38" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G38" s="8"/>
+      <c r="H38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A39" s="3">
+        <v>34</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E39" s="6"/>
+      <c r="F39" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G39" s="8"/>
+      <c r="H39" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I39" s="9"/>
+    </row>
+    <row r="40" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A40" s="3">
+        <v>35</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E40" s="6"/>
+      <c r="F40" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G40" s="8"/>
+      <c r="H40" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A41" s="3">
+        <v>36</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E41" s="6"/>
+      <c r="F41" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G41" s="8"/>
+      <c r="H41" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A42" s="3">
+        <v>37</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E42" s="6"/>
+      <c r="F42" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G42" s="8"/>
+      <c r="H42" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A43" s="3">
+        <v>38</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E43" s="6"/>
+      <c r="F43" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G43" s="8"/>
+      <c r="H43" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" s="9"/>
+    </row>
+    <row r="44" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A44" s="3">
+        <v>39</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E44" s="6"/>
+      <c r="F44" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G44" s="8"/>
+      <c r="H44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I44" s="9"/>
+    </row>
+    <row r="45" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A45" s="3">
+        <v>40</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" s="6"/>
+      <c r="F45" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G45" s="8"/>
+      <c r="H45" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I45" s="9"/>
+    </row>
+    <row r="46" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A46" s="3">
+        <v>41</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E46" s="6"/>
+      <c r="F46" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G46" s="8"/>
+      <c r="H46" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I46" s="9"/>
+    </row>
+    <row r="47" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A47" s="3">
+        <v>42</v>
+      </c>
+      <c r="B47" s="19"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E47" s="6"/>
+      <c r="F47" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G47" s="8"/>
+      <c r="H47" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="9"/>
+    </row>
+    <row r="48" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A48" s="3">
+        <v>43</v>
+      </c>
+      <c r="B48" s="19"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E48" s="6"/>
+      <c r="F48" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G48" s="8"/>
+      <c r="H48" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="9"/>
+    </row>
+    <row r="49" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A49" s="3">
+        <v>44</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E49" s="6"/>
+      <c r="F49" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G49" s="8"/>
+      <c r="H49" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" s="9"/>
+    </row>
+    <row r="50" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A50" s="3">
+        <v>45</v>
+      </c>
+      <c r="B50" s="19"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G50" s="8"/>
+      <c r="H50" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I50" s="9"/>
+    </row>
+    <row r="51" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A51" s="3">
+        <v>46</v>
+      </c>
+      <c r="B51" s="19"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E51" s="6"/>
+      <c r="F51" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G51" s="8"/>
+      <c r="H51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I51" s="9"/>
+    </row>
+    <row r="52" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A52" s="3">
+        <v>47</v>
+      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E52" s="6"/>
+      <c r="F52" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G52" s="8"/>
+      <c r="H52" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I52" s="9"/>
+    </row>
+    <row r="53" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A53" s="3">
+        <v>48</v>
+      </c>
+      <c r="B53" s="19"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" s="6"/>
+      <c r="F53" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G53" s="8"/>
+      <c r="H53" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I53" s="9"/>
+    </row>
+    <row r="54" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A54" s="3">
+        <v>49</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G54" s="8"/>
+      <c r="H54" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" s="9"/>
+    </row>
+    <row r="55" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A55" s="3">
+        <v>50</v>
+      </c>
+      <c r="B55" s="19"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E55" s="6"/>
+      <c r="F55" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G55" s="8"/>
+      <c r="H55" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" s="9"/>
+    </row>
+    <row r="56" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A56" s="3">
+        <v>51</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E56" s="6"/>
+      <c r="F56" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G56" s="8"/>
+      <c r="H56" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I56" s="9"/>
+    </row>
+    <row r="57" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A57" s="3">
+        <v>52</v>
+      </c>
+      <c r="B57" s="19"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E57" s="6"/>
+      <c r="F57" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G57" s="8"/>
+      <c r="H57" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" s="9"/>
+    </row>
+    <row r="58" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A58" s="3">
+        <v>53</v>
+      </c>
+      <c r="B58" s="19"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E58" s="6"/>
+      <c r="F58" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G58" s="8"/>
+      <c r="H58" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" s="9"/>
+    </row>
+    <row r="59" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A59" s="3">
+        <v>54</v>
+      </c>
+      <c r="B59" s="19"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E59" s="6"/>
+      <c r="F59" s="7">
+        <v>46241</v>
+      </c>
+      <c r="G59" s="8"/>
+      <c r="H59" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{888A0C2A-A619-4E0F-B7EE-5DA8152A3A62}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
